--- a/processed_data/hard_data_exports/hunt_tables/2026/2026_DEER_ANTLERLESS.xlsx
+++ b/processed_data/hard_data_exports/hunt_tables/2026/2026_DEER_ANTLERLESS.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026_deer_antlerless" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="2026_deer_antlerless" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026_deer_antlerless'!$A$3:$J$23</definedName>
@@ -539,7 +539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:N23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -614,6 +614,26 @@
           <t>Total</t>
         </is>
       </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>Harvest Prior Year</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>Harvest Success (Prior Year %)</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>Average Harvest Age (Prior Year)</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>Average Days Hunted (Prior Year)</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
@@ -658,6 +678,20 @@
           <t>30</t>
         </is>
       </c>
+      <c r="K4" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>22.7</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
@@ -702,6 +736,20 @@
           <t>30</t>
         </is>
       </c>
+      <c r="K5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>17.6</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="24" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
@@ -746,6 +794,20 @@
           <t>15</t>
         </is>
       </c>
+      <c r="K6" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>14.3</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2.7</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="24" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
@@ -790,6 +852,20 @@
           <t>25</t>
         </is>
       </c>
+      <c r="K7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
@@ -842,6 +918,20 @@
           <t>5</t>
         </is>
       </c>
+      <c r="K8" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="24" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
@@ -894,6 +984,20 @@
           <t>15</t>
         </is>
       </c>
+      <c r="K9" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>1.8</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="24" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
@@ -944,6 +1048,20 @@
       <c r="J10" s="6" t="inlineStr">
         <is>
           <t>5</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -990,6 +1108,20 @@
           <t>20</t>
         </is>
       </c>
+      <c r="K11" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>53.3</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="24" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
@@ -1034,6 +1166,20 @@
           <t>30</t>
         </is>
       </c>
+      <c r="K12" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>70.4</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2.7</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="24" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
@@ -1078,6 +1224,20 @@
           <t>25</t>
         </is>
       </c>
+      <c r="K13" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>14.3</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
@@ -1122,6 +1282,20 @@
           <t>20</t>
         </is>
       </c>
+      <c r="K14" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>73.3</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="24" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
@@ -1166,6 +1340,20 @@
           <t>5</t>
         </is>
       </c>
+      <c r="K15" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>1.8</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="24" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
@@ -1210,6 +1398,20 @@
           <t>15</t>
         </is>
       </c>
+      <c r="K16" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
@@ -1254,6 +1456,20 @@
           <t>5</t>
         </is>
       </c>
+      <c r="K17" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="24" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
@@ -1298,6 +1514,20 @@
           <t>20</t>
         </is>
       </c>
+      <c r="K18" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>41.7</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="24" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
@@ -1342,6 +1572,20 @@
           <t>25</t>
         </is>
       </c>
+      <c r="K19" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="24" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
@@ -1386,6 +1630,20 @@
           <t>25</t>
         </is>
       </c>
+      <c r="K20" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>26.7</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="24" customHeight="1">
       <c r="A21" s="7" t="inlineStr">
@@ -1430,6 +1688,20 @@
           <t>15</t>
         </is>
       </c>
+      <c r="K21" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="24" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
@@ -1474,6 +1746,20 @@
           <t>35</t>
         </is>
       </c>
+      <c r="K22" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>33.3</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>6.1</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="24" customHeight="1">
       <c r="A23" s="7" t="inlineStr">
@@ -1524,6 +1810,20 @@
       <c r="J23" s="8" t="inlineStr">
         <is>
           <t>8</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
